--- a/res/Card.xlsx
+++ b/res/Card.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\PythonWorkplace\Binary\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\PythonWorkplace\Probability\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99237714-C06B-436D-9AB4-EA1B1EC72F0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB2E67B-23DD-4684-8F40-C63A5EC7EF0F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000" xr2:uid="{51AAA0D9-229E-4E49-83B0-5342FE57A35A}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="61">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -199,7 +199,34 @@
     <t>type2</t>
   </si>
   <si>
-    <t>isTrue</t>
+    <t>tag1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>优选锦囊</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>锦囊</t>
+  </si>
+  <si>
+    <t>tag6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -207,7 +234,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="18"/>
       <color theme="1"/>
@@ -235,6 +262,20 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="vivo Sans"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="vivo Sans"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -253,12 +294,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -271,11 +315,48 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{34F31847-D318-41CD-8712-472539AD21AE}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -382,21 +463,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC005F87-753C-4035-AF28-88921D0D29EA}" name="表1_4" displayName="表1_4" ref="A1:M161" totalsRowShown="0">
-  <autoFilter ref="A1:M161" xr:uid="{516B080F-E782-44DC-9583-A7A64AC02D85}"/>
-  <sortState ref="A2:M161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC005F87-753C-4035-AF28-88921D0D29EA}" name="表1_4" displayName="表1_4" ref="A1:Q161" totalsRowShown="0">
+  <autoFilter ref="A1:Q161" xr:uid="{516B080F-E782-44DC-9583-A7A64AC02D85}"/>
+  <sortState ref="A2:Q161">
     <sortCondition ref="A1:A161"/>
   </sortState>
-  <tableColumns count="13">
+  <tableColumns count="17">
     <tableColumn id="12" xr3:uid="{64BBCE38-5936-4C87-AF10-3349147B669B}" name="id"/>
     <tableColumn id="2" xr3:uid="{2EB3C21C-5941-4E90-97BD-C27CBE419CE0}" name="name"/>
-    <tableColumn id="7" xr3:uid="{F4F1965D-5402-4058-98C7-57132F18887D}" name="color" dataDxfId="4"/>
-    <tableColumn id="30" xr3:uid="{C3FBF4DF-3C39-48B3-BF92-AE40DCD7AD9E}" name="color2" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{F4F1965D-5402-4058-98C7-57132F18887D}" name="color" dataDxfId="9"/>
+    <tableColumn id="30" xr3:uid="{C3FBF4DF-3C39-48B3-BF92-AE40DCD7AD9E}" name="color2" dataDxfId="8">
       <calculatedColumnFormula>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{20FEF319-AA80-4C81-B8DF-08C462A95C10}" name="number" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{8828C2AC-F1D7-4175-A020-E4B13A141F3A}" name="type" dataDxfId="1"/>
-    <tableColumn id="31" xr3:uid="{E02AAF82-DD05-43E9-8EFC-939F9579270A}" name="type2" dataDxfId="0">
+    <tableColumn id="6" xr3:uid="{20FEF319-AA80-4C81-B8DF-08C462A95C10}" name="number" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{8828C2AC-F1D7-4175-A020-E4B13A141F3A}" name="type" dataDxfId="6"/>
+    <tableColumn id="31" xr3:uid="{E02AAF82-DD05-43E9-8EFC-939F9579270A}" name="type2" dataDxfId="5">
       <calculatedColumnFormula>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{B2B49654-EE63-4B5E-A135-25E5EECF1BE2}" name="subType"/>
@@ -404,7 +485,11 @@
     <tableColumn id="9" xr3:uid="{4FF0B498-311B-4782-BACC-D5B8631F833A}" name="attDistance"/>
     <tableColumn id="10" xr3:uid="{BC677E26-FD68-45B3-B840-8749FEFDF591}" name="defDistance"/>
     <tableColumn id="11" xr3:uid="{A05B0A1A-53BB-4EFD-AC2D-FC62A816498E}" name="spellId"/>
-    <tableColumn id="1" xr3:uid="{FDE84897-1E68-41E5-9A90-9374A8ECFA32}" name="isTrue"/>
+    <tableColumn id="16" xr3:uid="{71E82C6F-E7AE-48BC-A3CC-E496035B7A55}" name="tag1" dataDxfId="1" dataCellStyle="常规 2"/>
+    <tableColumn id="14" xr3:uid="{24FA8482-2DA1-4C94-9658-7F9950F40513}" name="tag2" dataDxfId="0" dataCellStyle="常规 2"/>
+    <tableColumn id="1" xr3:uid="{FDE84897-1E68-41E5-9A90-9374A8ECFA32}" name="tag6" dataDxfId="4" dataCellStyle="常规 2"/>
+    <tableColumn id="5" xr3:uid="{EA75CDF4-DA26-4C8B-863C-05A8F20B9D60}" name="tag7" dataDxfId="3" dataCellStyle="常规 2"/>
+    <tableColumn id="13" xr3:uid="{F536AFA9-A8DD-4280-9630-7C55D8B0FC29}" name="tag8" dataDxfId="2" dataCellStyle="常规 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -613,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D04EA50-A07E-49F2-BF5D-56302F8712A2}">
-  <dimension ref="A1:M161"/>
+  <dimension ref="A1:Q161"/>
   <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.06640625" customWidth="1"/>
@@ -625,11 +710,10 @@
     <col min="7" max="7" width="5.73046875" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="7.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -669,8 +753,20 @@
       <c r="M1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="N1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P1" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -709,11 +805,17 @@
       <c r="L2">
         <v>8</v>
       </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -752,11 +854,13 @@
       <c r="L3">
         <v>2</v>
       </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M3" s="6"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -795,11 +899,17 @@
       <c r="L4">
         <v>4</v>
       </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -838,11 +948,17 @@
       <c r="L5">
         <v>4</v>
       </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M5" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -881,11 +997,13 @@
       <c r="L6">
         <v>28</v>
       </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M6" s="6"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -924,11 +1042,15 @@
       <c r="L7">
         <v>1</v>
       </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M7" s="6"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -967,11 +1089,15 @@
       <c r="L8">
         <v>1</v>
       </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M8" s="6"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1010,11 +1136,15 @@
       <c r="L9">
         <v>1</v>
       </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M9" s="6"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1053,11 +1183,15 @@
       <c r="L10">
         <v>1</v>
       </c>
-      <c r="M10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M10" s="6"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1096,11 +1230,15 @@
       <c r="L11">
         <v>1</v>
       </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M11" s="6"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1139,11 +1277,13 @@
       <c r="L12">
         <v>2</v>
       </c>
-      <c r="M12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M12" s="6"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1182,11 +1322,13 @@
       <c r="L13">
         <v>29</v>
       </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M13" s="6"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1225,11 +1367,13 @@
       <c r="L14">
         <v>18</v>
       </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M14" s="6"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1268,11 +1412,13 @@
       <c r="L15">
         <v>23</v>
       </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M15" s="6"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1311,11 +1457,13 @@
       <c r="L16">
         <v>2</v>
       </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M16" s="6"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1354,11 +1502,13 @@
       <c r="L17">
         <v>2</v>
       </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M17" s="6"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1397,11 +1547,13 @@
       <c r="L18">
         <v>2</v>
       </c>
-      <c r="M18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M18" s="6"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1440,11 +1592,13 @@
       <c r="L19">
         <v>2</v>
       </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M19" s="6"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1483,11 +1637,13 @@
       <c r="L20">
         <v>2</v>
       </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M20" s="6"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1526,11 +1682,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M21" s="6"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1569,11 +1727,13 @@
       <c r="L22">
         <v>2</v>
       </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M22" s="6"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1612,11 +1772,13 @@
       <c r="L23">
         <v>2</v>
       </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M23" s="6"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1655,11 +1817,13 @@
       <c r="L24">
         <v>2</v>
       </c>
-      <c r="M24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M24" s="6"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1698,11 +1862,13 @@
       <c r="L25">
         <v>2</v>
       </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M25" s="6"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1741,11 +1907,15 @@
       <c r="L26">
         <v>3</v>
       </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M26" s="6"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q26" s="4"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1784,11 +1954,15 @@
       <c r="L27">
         <v>1</v>
       </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M27" s="6"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1827,11 +2001,17 @@
       <c r="L28">
         <v>10</v>
       </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1870,11 +2050,13 @@
       <c r="L29">
         <v>2</v>
       </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M29" s="6"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1913,11 +2095,15 @@
       <c r="L30">
         <v>6</v>
       </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M30" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1956,11 +2142,15 @@
       <c r="L31">
         <v>6</v>
       </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M31" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1999,11 +2189,13 @@
       <c r="L32">
         <v>17</v>
       </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M32" s="6"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="4"/>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2042,11 +2234,15 @@
       <c r="L33">
         <v>15</v>
       </c>
-      <c r="M33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M33" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="4"/>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2085,11 +2281,17 @@
       <c r="L34">
         <v>7</v>
       </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M34" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4"/>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2128,11 +2330,17 @@
       <c r="L35">
         <v>7</v>
       </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M35" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N35" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2171,11 +2379,17 @@
       <c r="L36">
         <v>7</v>
       </c>
-      <c r="M36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M36" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O36" s="4"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2214,11 +2428,15 @@
       <c r="L37">
         <v>1</v>
       </c>
-      <c r="M37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M37" s="6"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2257,11 +2475,17 @@
       <c r="L38">
         <v>7</v>
       </c>
-      <c r="M38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M38" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N38" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O38" s="4"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2300,11 +2524,17 @@
       <c r="L39">
         <v>5</v>
       </c>
-      <c r="M39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M39" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N39" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2343,11 +2573,13 @@
       <c r="L40">
         <v>2</v>
       </c>
-      <c r="M40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M40" s="6"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="4"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2386,11 +2618,15 @@
       <c r="L41">
         <v>12</v>
       </c>
-      <c r="M41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M41" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2429,11 +2665,13 @@
       <c r="L42">
         <v>2</v>
       </c>
-      <c r="M42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M42" s="6"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2472,11 +2710,15 @@
       <c r="L43">
         <v>3</v>
       </c>
-      <c r="M43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M43" s="6"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q43" s="4"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2515,11 +2757,15 @@
       <c r="L44">
         <v>3</v>
       </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M44" s="6"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q44" s="4"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2558,11 +2804,13 @@
       <c r="L45">
         <v>30</v>
       </c>
-      <c r="M45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M45" s="6"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2601,11 +2849,15 @@
       <c r="L46">
         <v>3</v>
       </c>
-      <c r="M46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M46" s="6"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q46" s="4"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2644,11 +2896,15 @@
       <c r="L47">
         <v>3</v>
       </c>
-      <c r="M47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M47" s="6"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q47" s="4"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2687,11 +2943,15 @@
       <c r="L48">
         <v>3</v>
       </c>
-      <c r="M48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M48" s="6"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q48" s="4"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2730,11 +2990,15 @@
       <c r="L49">
         <v>3</v>
       </c>
-      <c r="M49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M49" s="6"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q49" s="4"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2773,11 +3037,15 @@
       <c r="L50">
         <v>1</v>
       </c>
-      <c r="M50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M50" s="6"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2816,11 +3084,15 @@
       <c r="L51">
         <v>1</v>
       </c>
-      <c r="M51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M51" s="6"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2859,11 +3131,15 @@
       <c r="L52">
         <v>3</v>
       </c>
-      <c r="M52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M52" s="6"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q52" s="4"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2902,11 +3178,13 @@
       <c r="L53">
         <v>22</v>
       </c>
-      <c r="M53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M53" s="6"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2945,11 +3223,17 @@
       <c r="L54">
         <v>8</v>
       </c>
-      <c r="M54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M54" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N54" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2988,11 +3272,15 @@
       <c r="L55">
         <v>1</v>
       </c>
-      <c r="M55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M55" s="6"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3031,11 +3319,15 @@
       <c r="L56">
         <v>1</v>
       </c>
-      <c r="M56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M56" s="6"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3074,11 +3366,15 @@
       <c r="L57">
         <v>1</v>
       </c>
-      <c r="M57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M57" s="6"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3117,11 +3413,15 @@
       <c r="L58">
         <v>1</v>
       </c>
-      <c r="M58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M58" s="6"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3160,11 +3460,15 @@
       <c r="L59">
         <v>1</v>
       </c>
-      <c r="M59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M59" s="6"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3203,11 +3507,15 @@
       <c r="L60">
         <v>1</v>
       </c>
-      <c r="M60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M60" s="6"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3246,11 +3554,15 @@
       <c r="L61">
         <v>1</v>
       </c>
-      <c r="M61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M61" s="6"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3289,11 +3601,15 @@
       <c r="L62">
         <v>1</v>
       </c>
-      <c r="M62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M62" s="6"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3332,11 +3648,15 @@
       <c r="L63">
         <v>1</v>
       </c>
-      <c r="M63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M63" s="6"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3375,11 +3695,15 @@
       <c r="L64">
         <v>1</v>
       </c>
-      <c r="M64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M64" s="6"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3418,11 +3742,15 @@
       <c r="L65">
         <v>13</v>
       </c>
-      <c r="M65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M65" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3461,11 +3789,15 @@
       <c r="L66">
         <v>13</v>
       </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M66" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3504,11 +3836,13 @@
       <c r="L67">
         <v>23</v>
       </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M67" s="6"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3547,11 +3881,13 @@
       <c r="L68">
         <v>16</v>
       </c>
-      <c r="M68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M68" s="6"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3590,11 +3926,17 @@
       <c r="L69">
         <v>5</v>
       </c>
-      <c r="M69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M69" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N69" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3633,11 +3975,17 @@
       <c r="L70">
         <v>5</v>
       </c>
-      <c r="M70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M70" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N70" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3676,11 +4024,13 @@
       <c r="L71">
         <v>21</v>
       </c>
-      <c r="M71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M71" s="6"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3719,11 +4069,15 @@
       <c r="L72">
         <v>15</v>
       </c>
-      <c r="M72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M72" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3762,11 +4116,17 @@
       <c r="L73">
         <v>9</v>
       </c>
-      <c r="M73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M73" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N73" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3805,11 +4165,15 @@
       <c r="L74">
         <v>1</v>
       </c>
-      <c r="M74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M74" s="6"/>
+      <c r="N74" s="4"/>
+      <c r="O74" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3848,11 +4212,15 @@
       <c r="L75">
         <v>1</v>
       </c>
-      <c r="M75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M75" s="6"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3891,11 +4259,15 @@
       <c r="L76">
         <v>1</v>
       </c>
-      <c r="M76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M76" s="6"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3934,11 +4306,15 @@
       <c r="L77">
         <v>1</v>
       </c>
-      <c r="M77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M77" s="6"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3977,11 +4353,15 @@
       <c r="L78">
         <v>14</v>
       </c>
-      <c r="M78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M78" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4020,11 +4400,15 @@
       <c r="L79">
         <v>14</v>
       </c>
-      <c r="M79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M79" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N79" s="4"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4063,11 +4447,17 @@
       <c r="L80">
         <v>8</v>
       </c>
-      <c r="M80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M80" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N80" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4106,11 +4496,13 @@
       <c r="L81">
         <v>24</v>
       </c>
-      <c r="M81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M81" s="6"/>
+      <c r="N81" s="4"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4149,11 +4541,17 @@
       <c r="L82">
         <v>4</v>
       </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M82" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N82" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4192,11 +4590,17 @@
       <c r="L83">
         <v>4</v>
       </c>
-      <c r="M83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M83" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N83" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4235,11 +4639,13 @@
       <c r="L84">
         <v>20</v>
       </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M84" s="6"/>
+      <c r="N84" s="4"/>
+      <c r="O84" s="4"/>
+      <c r="P84" s="4"/>
+      <c r="Q84" s="4"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4278,11 +4684,13 @@
       <c r="L85">
         <v>25</v>
       </c>
-      <c r="M85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M85" s="6"/>
+      <c r="N85" s="4"/>
+      <c r="O85" s="4"/>
+      <c r="P85" s="4"/>
+      <c r="Q85" s="4"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4321,11 +4729,15 @@
       <c r="L86">
         <v>1</v>
       </c>
-      <c r="M86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M86" s="6"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P86" s="4"/>
+      <c r="Q86" s="4"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4364,11 +4776,15 @@
       <c r="L87">
         <v>1</v>
       </c>
-      <c r="M87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M87" s="6"/>
+      <c r="N87" s="4"/>
+      <c r="O87" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P87" s="4"/>
+      <c r="Q87" s="4"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4407,11 +4823,15 @@
       <c r="L88">
         <v>1</v>
       </c>
-      <c r="M88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M88" s="6"/>
+      <c r="N88" s="4"/>
+      <c r="O88" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P88" s="4"/>
+      <c r="Q88" s="4"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4450,11 +4870,15 @@
       <c r="L89">
         <v>1</v>
       </c>
-      <c r="M89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M89" s="6"/>
+      <c r="N89" s="4"/>
+      <c r="O89" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P89" s="4"/>
+      <c r="Q89" s="4"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>89</v>
       </c>
@@ -4493,11 +4917,17 @@
       <c r="L90">
         <v>4</v>
       </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M90" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N90" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="4"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>90</v>
       </c>
@@ -4536,11 +4966,17 @@
       <c r="L91">
         <v>5</v>
       </c>
-      <c r="M91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M91" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N91" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>91</v>
       </c>
@@ -4579,11 +5015,17 @@
       <c r="L92">
         <v>9</v>
       </c>
-      <c r="M92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M92" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N92" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>92</v>
       </c>
@@ -4622,11 +5064,15 @@
       <c r="L93">
         <v>11</v>
       </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M93" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N93" s="4"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="4"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>93</v>
       </c>
@@ -4665,11 +5111,13 @@
       <c r="L94">
         <v>16</v>
       </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M94" s="6"/>
+      <c r="N94" s="4"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="4"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>94</v>
       </c>
@@ -4708,11 +5156,17 @@
       <c r="L95">
         <v>5</v>
       </c>
-      <c r="M95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M95" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N95" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>95</v>
       </c>
@@ -4751,11 +5205,17 @@
       <c r="L96">
         <v>5</v>
       </c>
-      <c r="M96">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M96" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N96" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>96</v>
       </c>
@@ -4794,11 +5254,13 @@
       <c r="L97">
         <v>26</v>
       </c>
-      <c r="M97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M97" s="6"/>
+      <c r="N97" s="4"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="4"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>97</v>
       </c>
@@ -4837,11 +5299,15 @@
       <c r="L98">
         <v>15</v>
       </c>
-      <c r="M98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M98" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="4"/>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>98</v>
       </c>
@@ -4880,11 +5346,17 @@
       <c r="L99">
         <v>9</v>
       </c>
-      <c r="M99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M99" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N99" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="4"/>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>99</v>
       </c>
@@ -4923,11 +5395,15 @@
       <c r="L100">
         <v>1</v>
       </c>
-      <c r="M100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M100" s="6"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>100</v>
       </c>
@@ -4966,11 +5442,15 @@
       <c r="L101">
         <v>1</v>
       </c>
-      <c r="M101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M101" s="6"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="4"/>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>101</v>
       </c>
@@ -5009,11 +5489,15 @@
       <c r="L102">
         <v>1</v>
       </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M102" s="6"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>102</v>
       </c>
@@ -5052,11 +5536,15 @@
       <c r="L103">
         <v>13</v>
       </c>
-      <c r="M103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M103" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>103</v>
       </c>
@@ -5095,11 +5583,13 @@
       <c r="L104">
         <v>27</v>
       </c>
-      <c r="M104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M104" s="6"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>104</v>
       </c>
@@ -5138,11 +5628,13 @@
       <c r="L105">
         <v>19</v>
       </c>
-      <c r="M105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M105" s="6"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="4"/>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>105</v>
       </c>
@@ -5181,11 +5673,15 @@
       <c r="L106">
         <v>11</v>
       </c>
-      <c r="M106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M106" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>106</v>
       </c>
@@ -5224,11 +5720,15 @@
       <c r="L107">
         <v>13</v>
       </c>
-      <c r="M107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M107" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>107</v>
       </c>
@@ -5267,11 +5767,13 @@
       <c r="L108">
         <v>200</v>
       </c>
-      <c r="M108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M108" s="6"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>108</v>
       </c>
@@ -5310,11 +5812,13 @@
       <c r="L109">
         <v>201</v>
       </c>
-      <c r="M109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M109" s="6"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>109</v>
       </c>
@@ -5353,11 +5857,15 @@
       <c r="L110">
         <v>13</v>
       </c>
-      <c r="M110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M110" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>110</v>
       </c>
@@ -5396,11 +5904,17 @@
       <c r="L111">
         <v>83</v>
       </c>
-      <c r="M111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M111" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N111" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>111</v>
       </c>
@@ -5439,11 +5953,17 @@
       <c r="L112">
         <v>83</v>
       </c>
-      <c r="M112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M112" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N112" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="4"/>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>112</v>
       </c>
@@ -5482,11 +6002,15 @@
       <c r="L113">
         <v>1</v>
       </c>
-      <c r="M113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M113" s="6"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>113</v>
       </c>
@@ -5525,11 +6049,15 @@
       <c r="L114">
         <v>3</v>
       </c>
-      <c r="M114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M114" s="6"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q114" s="4"/>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>114</v>
       </c>
@@ -5568,11 +6096,15 @@
       <c r="L115">
         <v>3</v>
       </c>
-      <c r="M115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M115" s="6"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q115" s="4"/>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>115</v>
       </c>
@@ -5611,11 +6143,15 @@
       <c r="L116">
         <v>1</v>
       </c>
-      <c r="M116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M116" s="6"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="4"/>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>116</v>
       </c>
@@ -5654,11 +6190,13 @@
       <c r="L117">
         <v>2</v>
       </c>
-      <c r="M117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M117" s="6"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="4"/>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>117</v>
       </c>
@@ -5697,11 +6235,13 @@
       <c r="L118">
         <v>2</v>
       </c>
-      <c r="M118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M118" s="6"/>
+      <c r="N118" s="4"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>118</v>
       </c>
@@ -5740,11 +6280,15 @@
       <c r="L119">
         <v>1</v>
       </c>
-      <c r="M119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M119" s="6"/>
+      <c r="N119" s="4"/>
+      <c r="O119" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P119" s="4"/>
+      <c r="Q119" s="4"/>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>119</v>
       </c>
@@ -5783,11 +6327,13 @@
       <c r="L120">
         <v>2</v>
       </c>
-      <c r="M120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M120" s="6"/>
+      <c r="N120" s="4"/>
+      <c r="O120" s="4"/>
+      <c r="P120" s="4"/>
+      <c r="Q120" s="4"/>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>120</v>
       </c>
@@ -5826,11 +6372,13 @@
       <c r="L121">
         <v>2</v>
       </c>
-      <c r="M121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M121" s="6"/>
+      <c r="N121" s="4"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="4"/>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>121</v>
       </c>
@@ -5869,11 +6417,15 @@
       <c r="L122">
         <v>13</v>
       </c>
-      <c r="M122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M122" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N122" s="4"/>
+      <c r="O122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="4"/>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>122</v>
       </c>
@@ -5912,11 +6464,13 @@
       <c r="L123">
         <v>87</v>
       </c>
-      <c r="M123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M123" s="6"/>
+      <c r="N123" s="4"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="4"/>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>123</v>
       </c>
@@ -5955,11 +6509,15 @@
       <c r="L124">
         <v>3</v>
       </c>
-      <c r="M124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M124" s="6"/>
+      <c r="N124" s="4"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q124" s="4"/>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>124</v>
       </c>
@@ -5998,11 +6556,15 @@
       <c r="L125">
         <v>3</v>
       </c>
-      <c r="M125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M125" s="6"/>
+      <c r="N125" s="4"/>
+      <c r="O125" s="4"/>
+      <c r="P125" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q125" s="4"/>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>125</v>
       </c>
@@ -6041,11 +6603,15 @@
       <c r="L126">
         <v>1</v>
       </c>
-      <c r="M126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M126" s="6"/>
+      <c r="N126" s="4"/>
+      <c r="O126" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P126" s="4"/>
+      <c r="Q126" s="4"/>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>126</v>
       </c>
@@ -6084,11 +6650,15 @@
       <c r="L127">
         <v>1</v>
       </c>
-      <c r="M127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M127" s="6"/>
+      <c r="N127" s="4"/>
+      <c r="O127" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P127" s="4"/>
+      <c r="Q127" s="4"/>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>127</v>
       </c>
@@ -6127,11 +6697,13 @@
       <c r="L128">
         <v>2</v>
       </c>
-      <c r="M128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M128" s="6"/>
+      <c r="N128" s="4"/>
+      <c r="O128" s="4"/>
+      <c r="P128" s="4"/>
+      <c r="Q128" s="4"/>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>128</v>
       </c>
@@ -6170,11 +6742,13 @@
       <c r="L129">
         <v>2</v>
       </c>
-      <c r="M129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M129" s="6"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="4"/>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>129</v>
       </c>
@@ -6213,11 +6787,13 @@
       <c r="L130">
         <v>2</v>
       </c>
-      <c r="M130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M130" s="6"/>
+      <c r="N130" s="4"/>
+      <c r="O130" s="4"/>
+      <c r="P130" s="4"/>
+      <c r="Q130" s="4"/>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>130</v>
       </c>
@@ -6256,11 +6832,15 @@
       <c r="L131">
         <v>82</v>
       </c>
-      <c r="M131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M131" s="6"/>
+      <c r="N131" s="4"/>
+      <c r="O131" s="4"/>
+      <c r="P131" s="4"/>
+      <c r="Q131" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>131</v>
       </c>
@@ -6299,11 +6879,13 @@
       <c r="L132">
         <v>2</v>
       </c>
-      <c r="M132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M132" s="6"/>
+      <c r="N132" s="4"/>
+      <c r="O132" s="4"/>
+      <c r="P132" s="4"/>
+      <c r="Q132" s="4"/>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>132</v>
       </c>
@@ -6342,11 +6924,13 @@
       <c r="L133">
         <v>2</v>
       </c>
-      <c r="M133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M133" s="6"/>
+      <c r="N133" s="4"/>
+      <c r="O133" s="4"/>
+      <c r="P133" s="4"/>
+      <c r="Q133" s="4"/>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>133</v>
       </c>
@@ -6385,11 +6969,17 @@
       <c r="L134">
         <v>83</v>
       </c>
-      <c r="M134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M134" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N134" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O134" s="4"/>
+      <c r="P134" s="4"/>
+      <c r="Q134" s="4"/>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>134</v>
       </c>
@@ -6428,11 +7018,13 @@
       <c r="L135">
         <v>90</v>
       </c>
-      <c r="M135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M135" s="6"/>
+      <c r="N135" s="4"/>
+      <c r="O135" s="4"/>
+      <c r="P135" s="4"/>
+      <c r="Q135" s="4"/>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>135</v>
       </c>
@@ -6471,11 +7063,13 @@
       <c r="L136">
         <v>86</v>
       </c>
-      <c r="M136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M136" s="6"/>
+      <c r="N136" s="4"/>
+      <c r="O136" s="4"/>
+      <c r="P136" s="4"/>
+      <c r="Q136" s="4"/>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>136</v>
       </c>
@@ -6514,11 +7108,13 @@
       <c r="L137">
         <v>88</v>
       </c>
-      <c r="M137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M137" s="6"/>
+      <c r="N137" s="4"/>
+      <c r="O137" s="4"/>
+      <c r="P137" s="4"/>
+      <c r="Q137" s="4"/>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>137</v>
       </c>
@@ -6557,11 +7153,15 @@
       <c r="L138">
         <v>82</v>
       </c>
-      <c r="M138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M138" s="6"/>
+      <c r="N138" s="4"/>
+      <c r="O138" s="4"/>
+      <c r="P138" s="4"/>
+      <c r="Q138" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>138</v>
       </c>
@@ -6600,11 +7200,15 @@
       <c r="L139">
         <v>1</v>
       </c>
-      <c r="M139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M139" s="6"/>
+      <c r="N139" s="4"/>
+      <c r="O139" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P139" s="4"/>
+      <c r="Q139" s="4"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>139</v>
       </c>
@@ -6643,11 +7247,15 @@
       <c r="L140">
         <v>1</v>
       </c>
-      <c r="M140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M140" s="6"/>
+      <c r="N140" s="4"/>
+      <c r="O140" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P140" s="4"/>
+      <c r="Q140" s="4"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>140</v>
       </c>
@@ -6686,11 +7294,15 @@
       <c r="L141">
         <v>1</v>
       </c>
-      <c r="M141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M141" s="6"/>
+      <c r="N141" s="4"/>
+      <c r="O141" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P141" s="4"/>
+      <c r="Q141" s="4"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>141</v>
       </c>
@@ -6729,11 +7341,15 @@
       <c r="L142">
         <v>1</v>
       </c>
-      <c r="M142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M142" s="6"/>
+      <c r="N142" s="4"/>
+      <c r="O142" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P142" s="4"/>
+      <c r="Q142" s="4"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>142</v>
       </c>
@@ -6772,11 +7388,15 @@
       <c r="L143">
         <v>1</v>
       </c>
-      <c r="M143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M143" s="6"/>
+      <c r="N143" s="4"/>
+      <c r="O143" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P143" s="4"/>
+      <c r="Q143" s="4"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>143</v>
       </c>
@@ -6815,11 +7435,15 @@
       <c r="L144">
         <v>82</v>
       </c>
-      <c r="M144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M144" s="6"/>
+      <c r="N144" s="4"/>
+      <c r="O144" s="4"/>
+      <c r="P144" s="4"/>
+      <c r="Q144" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>144</v>
       </c>
@@ -6858,11 +7482,15 @@
       <c r="L145">
         <v>84</v>
       </c>
-      <c r="M145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M145" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N145" s="4"/>
+      <c r="O145" s="4"/>
+      <c r="P145" s="4"/>
+      <c r="Q145" s="4"/>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>145</v>
       </c>
@@ -6901,11 +7529,15 @@
       <c r="L146">
         <v>85</v>
       </c>
-      <c r="M146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M146" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N146" s="4"/>
+      <c r="O146" s="4"/>
+      <c r="P146" s="4"/>
+      <c r="Q146" s="4"/>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>146</v>
       </c>
@@ -6944,11 +7576,15 @@
       <c r="L147">
         <v>85</v>
       </c>
-      <c r="M147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M147" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N147" s="4"/>
+      <c r="O147" s="4"/>
+      <c r="P147" s="4"/>
+      <c r="Q147" s="4"/>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>147</v>
       </c>
@@ -6987,11 +7623,15 @@
       <c r="L148">
         <v>13</v>
       </c>
-      <c r="M148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M148" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N148" s="4"/>
+      <c r="O148" s="4"/>
+      <c r="P148" s="4"/>
+      <c r="Q148" s="4"/>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>148</v>
       </c>
@@ -7030,11 +7670,13 @@
       <c r="L149">
         <v>89</v>
       </c>
-      <c r="M149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M149" s="6"/>
+      <c r="N149" s="4"/>
+      <c r="O149" s="4"/>
+      <c r="P149" s="4"/>
+      <c r="Q149" s="4"/>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>149</v>
       </c>
@@ -7073,11 +7715,13 @@
       <c r="L150">
         <v>88</v>
       </c>
-      <c r="M150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M150" s="6"/>
+      <c r="N150" s="4"/>
+      <c r="O150" s="4"/>
+      <c r="P150" s="4"/>
+      <c r="Q150" s="4"/>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>150</v>
       </c>
@@ -7116,11 +7760,15 @@
       <c r="L151">
         <v>82</v>
       </c>
-      <c r="M151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M151" s="6"/>
+      <c r="N151" s="4"/>
+      <c r="O151" s="4"/>
+      <c r="P151" s="4"/>
+      <c r="Q151" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>151</v>
       </c>
@@ -7159,11 +7807,15 @@
       <c r="L152">
         <v>84</v>
       </c>
-      <c r="M152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M152" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N152" s="4"/>
+      <c r="O152" s="4"/>
+      <c r="P152" s="4"/>
+      <c r="Q152" s="4"/>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>152</v>
       </c>
@@ -7202,11 +7854,15 @@
       <c r="L153">
         <v>1</v>
       </c>
-      <c r="M153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M153" s="6"/>
+      <c r="N153" s="4"/>
+      <c r="O153" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P153" s="4"/>
+      <c r="Q153" s="4"/>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>153</v>
       </c>
@@ -7245,11 +7901,15 @@
       <c r="L154">
         <v>1</v>
       </c>
-      <c r="M154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M154" s="6"/>
+      <c r="N154" s="4"/>
+      <c r="O154" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="4"/>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>154</v>
       </c>
@@ -7288,11 +7948,15 @@
       <c r="L155">
         <v>1</v>
       </c>
-      <c r="M155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M155" s="6"/>
+      <c r="N155" s="4"/>
+      <c r="O155" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P155" s="4"/>
+      <c r="Q155" s="4"/>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>155</v>
       </c>
@@ -7331,11 +7995,15 @@
       <c r="L156">
         <v>1</v>
       </c>
-      <c r="M156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M156" s="6"/>
+      <c r="N156" s="4"/>
+      <c r="O156" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P156" s="4"/>
+      <c r="Q156" s="4"/>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>156</v>
       </c>
@@ -7374,11 +8042,15 @@
       <c r="L157">
         <v>82</v>
       </c>
-      <c r="M157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M157" s="6"/>
+      <c r="N157" s="4"/>
+      <c r="O157" s="4"/>
+      <c r="P157" s="4"/>
+      <c r="Q157" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>157</v>
       </c>
@@ -7417,11 +8089,15 @@
       <c r="L158">
         <v>85</v>
       </c>
-      <c r="M158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M158" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N158" s="4"/>
+      <c r="O158" s="4"/>
+      <c r="P158" s="4"/>
+      <c r="Q158" s="4"/>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>158</v>
       </c>
@@ -7460,11 +8136,15 @@
       <c r="L159">
         <v>85</v>
       </c>
-      <c r="M159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M159" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N159" s="4"/>
+      <c r="O159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="4"/>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>159</v>
       </c>
@@ -7503,11 +8183,15 @@
       <c r="L160">
         <v>85</v>
       </c>
-      <c r="M160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M160" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N160" s="4"/>
+      <c r="O160" s="4"/>
+      <c r="P160" s="4"/>
+      <c r="Q160" s="4"/>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>160</v>
       </c>
@@ -7546,9 +8230,13 @@
       <c r="L161">
         <v>85</v>
       </c>
-      <c r="M161">
-        <v>0</v>
-      </c>
+      <c r="M161" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N161" s="4"/>
+      <c r="O161" s="4"/>
+      <c r="P161" s="4"/>
+      <c r="Q161" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/res/Card.xlsx
+++ b/res/Card.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bread\Workplace\Python\Binary\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workplace\PythonWorkplace\Probability\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2512FE2-B250-453C-A615-F3EC4C1F40E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CFA7F2-831C-4D13-8395-FA169C80AEC2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{51AAA0D9-229E-4E49-83B0-5342FE57A35A}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="41490" windowHeight="16770" xr2:uid="{51AAA0D9-229E-4E49-83B0-5342FE57A35A}"/>
   </bookViews>
   <sheets>
     <sheet name="160" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -44,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="65">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,14 +208,48 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>伤害锦囊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>tag2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>锦囊</t>
+  </si>
+  <si>
+    <t>优选锦囊</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>颅行</t>
+  </si>
+  <si>
+    <t>tag3</t>
+  </si>
+  <si>
+    <t>tag4</t>
+  </si>
+  <si>
+    <t>tag5</t>
+  </si>
+  <si>
+    <t>tag6</t>
+  </si>
+  <si>
+    <t>tag7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="18"/>
       <color theme="1"/>
@@ -261,6 +284,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="vivo Sans"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -287,7 +317,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -303,12 +333,27 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{34F31847-D318-41CD-8712-472539AD21AE}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -424,21 +469,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC005F87-753C-4035-AF28-88921D0D29EA}" name="表1_4" displayName="表1_4" ref="A1:M161" totalsRowShown="0">
-  <autoFilter ref="A1:M161" xr:uid="{516B080F-E782-44DC-9583-A7A64AC02D85}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC005F87-753C-4035-AF28-88921D0D29EA}" name="表1_4" displayName="表1_4" ref="A1:S161" totalsRowShown="0">
+  <autoFilter ref="A1:S161" xr:uid="{516B080F-E782-44DC-9583-A7A64AC02D85}"/>
+  <sortState ref="A2:S161">
     <sortCondition ref="B1:B161"/>
   </sortState>
-  <tableColumns count="13">
+  <tableColumns count="19">
     <tableColumn id="12" xr3:uid="{64BBCE38-5936-4C87-AF10-3349147B669B}" name="id"/>
     <tableColumn id="2" xr3:uid="{2EB3C21C-5941-4E90-97BD-C27CBE419CE0}" name="name"/>
-    <tableColumn id="7" xr3:uid="{F4F1965D-5402-4058-98C7-57132F18887D}" name="color" dataDxfId="5"/>
-    <tableColumn id="30" xr3:uid="{C3FBF4DF-3C39-48B3-BF92-AE40DCD7AD9E}" name="color2" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{F4F1965D-5402-4058-98C7-57132F18887D}" name="color" dataDxfId="6"/>
+    <tableColumn id="30" xr3:uid="{C3FBF4DF-3C39-48B3-BF92-AE40DCD7AD9E}" name="color2" dataDxfId="5">
       <calculatedColumnFormula>_xlfn.SWITCH(表1_4[[#This Row],[color]],1,"♥",2,"♦",3,"♠",4,"♣")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{20FEF319-AA80-4C81-B8DF-08C462A95C10}" name="number" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{8828C2AC-F1D7-4175-A020-E4B13A141F3A}" name="type" dataDxfId="2"/>
-    <tableColumn id="31" xr3:uid="{E02AAF82-DD05-43E9-8EFC-939F9579270A}" name="type2" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{20FEF319-AA80-4C81-B8DF-08C462A95C10}" name="number" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{8828C2AC-F1D7-4175-A020-E4B13A141F3A}" name="type" dataDxfId="3"/>
+    <tableColumn id="31" xr3:uid="{E02AAF82-DD05-43E9-8EFC-939F9579270A}" name="type2" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.SWITCH(表1_4[[#This Row],[type]],1,"基本",2,"锦囊",3,"装备")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{B2B49654-EE63-4B5E-A135-25E5EECF1BE2}" name="subType"/>
@@ -446,7 +491,13 @@
     <tableColumn id="9" xr3:uid="{4FF0B498-311B-4782-BACC-D5B8631F833A}" name="attDistance"/>
     <tableColumn id="10" xr3:uid="{BC677E26-FD68-45B3-B840-8749FEFDF591}" name="defDistance"/>
     <tableColumn id="11" xr3:uid="{A05B0A1A-53BB-4EFD-AC2D-FC62A816498E}" name="spellId"/>
-    <tableColumn id="16" xr3:uid="{71E82C6F-E7AE-48BC-A3CC-E496035B7A55}" name="tag1" dataDxfId="0" dataCellStyle="常规 2"/>
+    <tableColumn id="16" xr3:uid="{71E82C6F-E7AE-48BC-A3CC-E496035B7A55}" name="tag1" dataDxfId="1" dataCellStyle="常规 2"/>
+    <tableColumn id="1" xr3:uid="{F283226C-E65D-47E8-855F-F2596C1A4A64}" name="tag2" dataDxfId="0" dataCellStyle="常规 2"/>
+    <tableColumn id="5" xr3:uid="{F3904A53-EBC2-474B-AE0A-4A95B2FDF449}" name="tag3"/>
+    <tableColumn id="13" xr3:uid="{455EA8D3-B7C2-4014-83E6-00B612B8A8C5}" name="tag4"/>
+    <tableColumn id="14" xr3:uid="{A62BAADB-239E-4EF4-BADE-E4659C4531DE}" name="tag5"/>
+    <tableColumn id="15" xr3:uid="{534E17C0-2147-412A-B0C1-8C7642F9F51F}" name="tag6"/>
+    <tableColumn id="17" xr3:uid="{2EB54EF8-E09E-47BD-8EA5-959DD78633F8}" name="tag7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -655,22 +706,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D04EA50-A07E-49F2-BF5D-56302F8712A2}">
-  <dimension ref="A1:M161"/>
-  <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:S161"/>
+  <sheetFormatPr defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.05078125" customWidth="1"/>
-    <col min="2" max="2" width="12.41796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.05078125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.68359375" customWidth="1"/>
-    <col min="5" max="5" width="3.41796875" customWidth="1"/>
-    <col min="6" max="6" width="5.734375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.734375" customWidth="1"/>
+    <col min="1" max="1" width="6.06640625" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.06640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" customWidth="1"/>
+    <col min="6" max="6" width="5.73046875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.3125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5234375" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>50</v>
       </c>
@@ -707,11 +758,29 @@
       <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" t="s">
+        <v>60</v>
+      </c>
+      <c r="P1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>62</v>
+      </c>
+      <c r="R1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>67</v>
       </c>
@@ -750,9 +819,14 @@
       <c r="L2">
         <v>16</v>
       </c>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N2" s="6"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>93</v>
       </c>
@@ -791,9 +865,14 @@
       <c r="L3">
         <v>16</v>
       </c>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N3" s="6"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>148</v>
       </c>
@@ -832,9 +911,9 @@
       <c r="L4">
         <v>89</v>
       </c>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>144</v>
       </c>
@@ -873,9 +952,9 @@
       <c r="L5">
         <v>84</v>
       </c>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>151</v>
       </c>
@@ -914,9 +993,9 @@
       <c r="L6">
         <v>84</v>
       </c>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>31</v>
       </c>
@@ -955,9 +1034,14 @@
       <c r="L7">
         <v>17</v>
       </c>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N7" s="6"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>80</v>
       </c>
@@ -996,9 +1080,14 @@
       <c r="L8">
         <v>24</v>
       </c>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N8" s="6"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>104</v>
       </c>
@@ -1037,9 +1126,14 @@
       <c r="L9">
         <v>19</v>
       </c>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N9" s="6"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>70</v>
       </c>
@@ -1078,9 +1172,14 @@
       <c r="L10">
         <v>21</v>
       </c>
-      <c r="M10" s="4"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N10" s="6"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>12</v>
       </c>
@@ -1119,9 +1218,14 @@
       <c r="L11">
         <v>29</v>
       </c>
-      <c r="M11" s="4"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N11" s="6"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>135</v>
       </c>
@@ -1160,9 +1264,9 @@
       <c r="L12">
         <v>86</v>
       </c>
-      <c r="M12" s="4"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1201,9 +1305,14 @@
       <c r="L13">
         <v>28</v>
       </c>
-      <c r="M13" s="4"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N13" s="6"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>38</v>
       </c>
@@ -1242,11 +1351,21 @@
       <c r="L14">
         <v>5</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M14" s="5"/>
+      <c r="N14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>68</v>
       </c>
@@ -1285,11 +1404,21 @@
       <c r="L15">
         <v>5</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M15" s="5"/>
+      <c r="N15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P15" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>69</v>
       </c>
@@ -1328,11 +1457,21 @@
       <c r="L16">
         <v>5</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M16" s="5"/>
+      <c r="N16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>90</v>
       </c>
@@ -1371,11 +1510,21 @@
       <c r="L17">
         <v>5</v>
       </c>
-      <c r="M17" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M17" s="5"/>
+      <c r="N17" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>94</v>
       </c>
@@ -1414,11 +1563,21 @@
       <c r="L18">
         <v>5</v>
       </c>
-      <c r="M18" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M18" s="5"/>
+      <c r="N18" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>95</v>
       </c>
@@ -1457,11 +1616,21 @@
       <c r="L19">
         <v>5</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M19" s="5"/>
+      <c r="N19" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>108</v>
       </c>
@@ -1500,9 +1669,14 @@
       <c r="L20">
         <v>201</v>
       </c>
-      <c r="M20" s="4"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N20" s="6"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>134</v>
       </c>
@@ -1541,9 +1715,9 @@
       <c r="L21">
         <v>90</v>
       </c>
-      <c r="M21" s="4"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>110</v>
       </c>
@@ -1582,9 +1756,21 @@
       <c r="L22">
         <v>83</v>
       </c>
-      <c r="M22" s="4"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N22" s="6"/>
+      <c r="O22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P22" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>111</v>
       </c>
@@ -1623,9 +1809,21 @@
       <c r="L23">
         <v>83</v>
       </c>
-      <c r="M23" s="4"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" s="6"/>
+      <c r="O23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>133</v>
       </c>
@@ -1664,9 +1862,12 @@
       <c r="L24">
         <v>83</v>
       </c>
-      <c r="M24" s="4"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>77</v>
       </c>
@@ -1705,9 +1906,17 @@
       <c r="L25">
         <v>14</v>
       </c>
-      <c r="M25" s="4"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M25" s="5"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>78</v>
       </c>
@@ -1746,9 +1955,17 @@
       <c r="L26">
         <v>14</v>
       </c>
-      <c r="M26" s="4"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M26" s="5"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>130</v>
       </c>
@@ -1787,9 +2004,16 @@
       <c r="L27">
         <v>82</v>
       </c>
-      <c r="M27" s="4"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N27" s="6"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>137</v>
       </c>
@@ -1828,9 +2052,9 @@
       <c r="L28">
         <v>82</v>
       </c>
-      <c r="M28" s="4"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>143</v>
       </c>
@@ -1869,9 +2093,9 @@
       <c r="L29">
         <v>82</v>
       </c>
-      <c r="M29" s="4"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>150</v>
       </c>
@@ -1910,9 +2134,9 @@
       <c r="L30">
         <v>82</v>
       </c>
-      <c r="M30" s="4"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>156</v>
       </c>
@@ -1951,9 +2175,9 @@
       <c r="L31">
         <v>82</v>
       </c>
-      <c r="M31" s="4"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1</v>
       </c>
@@ -1992,9 +2216,21 @@
       <c r="L32">
         <v>8</v>
       </c>
-      <c r="M32" s="4"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M32" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" s="6"/>
+      <c r="O32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>53</v>
       </c>
@@ -2033,9 +2269,21 @@
       <c r="L33">
         <v>8</v>
       </c>
-      <c r="M33" s="4"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N33" s="6"/>
+      <c r="O33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>79</v>
       </c>
@@ -2074,9 +2322,21 @@
       <c r="L34">
         <v>8</v>
       </c>
-      <c r="M34" s="4"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M34" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" s="6"/>
+      <c r="O34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P34" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>83</v>
       </c>
@@ -2115,9 +2375,14 @@
       <c r="L35">
         <v>20</v>
       </c>
-      <c r="M35" s="4"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N35" s="6"/>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>32</v>
       </c>
@@ -2156,9 +2421,17 @@
       <c r="L36">
         <v>15</v>
       </c>
-      <c r="M36" s="4"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M36" s="5"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>71</v>
       </c>
@@ -2197,9 +2470,17 @@
       <c r="L37">
         <v>15</v>
       </c>
-      <c r="M37" s="4"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M37" s="5"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>97</v>
       </c>
@@ -2238,9 +2519,17 @@
       <c r="L38">
         <v>15</v>
       </c>
-      <c r="M38" s="4"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M38" s="5"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>72</v>
       </c>
@@ -2279,9 +2568,21 @@
       <c r="L39">
         <v>9</v>
       </c>
-      <c r="M39" s="4"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M39" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N39" s="6"/>
+      <c r="O39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>91</v>
       </c>
@@ -2320,9 +2621,21 @@
       <c r="L40">
         <v>9</v>
       </c>
-      <c r="M40" s="4"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M40" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N40" s="6"/>
+      <c r="O40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P40" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>98</v>
       </c>
@@ -2361,9 +2674,21 @@
       <c r="L41">
         <v>9</v>
       </c>
-      <c r="M41" s="4"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M41" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N41" s="6"/>
+      <c r="O41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P41" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>44</v>
       </c>
@@ -2402,9 +2727,14 @@
       <c r="L42">
         <v>30</v>
       </c>
-      <c r="M42" s="4"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N42" s="6"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>84</v>
       </c>
@@ -2443,9 +2773,14 @@
       <c r="L43">
         <v>25</v>
       </c>
-      <c r="M43" s="4"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N43" s="6"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>96</v>
       </c>
@@ -2484,9 +2819,14 @@
       <c r="L44">
         <v>26</v>
       </c>
-      <c r="M44" s="4"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N44" s="6"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>107</v>
       </c>
@@ -2525,9 +2865,14 @@
       <c r="L45">
         <v>200</v>
       </c>
-      <c r="M45" s="4"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N45" s="6"/>
+      <c r="O45" s="4"/>
+      <c r="P45" s="4"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>6</v>
       </c>
@@ -2566,9 +2911,16 @@
       <c r="L46">
         <v>1</v>
       </c>
-      <c r="M46" s="4"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N46" s="6"/>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>7</v>
       </c>
@@ -2607,9 +2959,16 @@
       <c r="L47">
         <v>1</v>
       </c>
-      <c r="M47" s="4"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N47" s="6"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>8</v>
       </c>
@@ -2648,9 +3007,16 @@
       <c r="L48">
         <v>1</v>
       </c>
-      <c r="M48" s="4"/>
-    </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N48" s="6"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>9</v>
       </c>
@@ -2689,9 +3055,16 @@
       <c r="L49">
         <v>1</v>
       </c>
-      <c r="M49" s="4"/>
-    </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N49" s="6"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>10</v>
       </c>
@@ -2730,9 +3103,16 @@
       <c r="L50">
         <v>1</v>
       </c>
-      <c r="M50" s="4"/>
-    </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N50" s="6"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>26</v>
       </c>
@@ -2771,9 +3151,16 @@
       <c r="L51">
         <v>1</v>
       </c>
-      <c r="M51" s="4"/>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N51" s="6"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>36</v>
       </c>
@@ -2812,9 +3199,16 @@
       <c r="L52">
         <v>1</v>
       </c>
-      <c r="M52" s="4"/>
-    </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N52" s="6"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>49</v>
       </c>
@@ -2853,9 +3247,16 @@
       <c r="L53">
         <v>1</v>
       </c>
-      <c r="M53" s="4"/>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N53" s="6"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>50</v>
       </c>
@@ -2894,9 +3295,16 @@
       <c r="L54">
         <v>1</v>
       </c>
-      <c r="M54" s="4"/>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N54" s="6"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2935,9 +3343,16 @@
       <c r="L55">
         <v>1</v>
       </c>
-      <c r="M55" s="4"/>
-    </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N55" s="6"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2976,9 +3391,16 @@
       <c r="L56">
         <v>1</v>
       </c>
-      <c r="M56" s="4"/>
-    </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N56" s="6"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3017,9 +3439,16 @@
       <c r="L57">
         <v>1</v>
       </c>
-      <c r="M57" s="4"/>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N57" s="6"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3058,9 +3487,16 @@
       <c r="L58">
         <v>1</v>
       </c>
-      <c r="M58" s="4"/>
-    </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N58" s="6"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3099,9 +3535,16 @@
       <c r="L59">
         <v>1</v>
       </c>
-      <c r="M59" s="4"/>
-    </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N59" s="6"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3140,9 +3583,16 @@
       <c r="L60">
         <v>1</v>
       </c>
-      <c r="M60" s="4"/>
-    </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N60" s="6"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3181,9 +3631,16 @@
       <c r="L61">
         <v>1</v>
       </c>
-      <c r="M61" s="4"/>
-    </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N61" s="6"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3222,9 +3679,16 @@
       <c r="L62">
         <v>1</v>
       </c>
-      <c r="M62" s="4"/>
-    </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N62" s="6"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3263,9 +3727,16 @@
       <c r="L63">
         <v>1</v>
       </c>
-      <c r="M63" s="4"/>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N63" s="6"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3304,9 +3775,16 @@
       <c r="L64">
         <v>1</v>
       </c>
-      <c r="M64" s="4"/>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N64" s="6"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>73</v>
       </c>
@@ -3345,9 +3823,16 @@
       <c r="L65">
         <v>1</v>
       </c>
-      <c r="M65" s="4"/>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N65" s="6"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>74</v>
       </c>
@@ -3386,9 +3871,16 @@
       <c r="L66">
         <v>1</v>
       </c>
-      <c r="M66" s="4"/>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N66" s="6"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>75</v>
       </c>
@@ -3427,9 +3919,16 @@
       <c r="L67">
         <v>1</v>
       </c>
-      <c r="M67" s="4"/>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N67" s="6"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>76</v>
       </c>
@@ -3468,9 +3967,16 @@
       <c r="L68">
         <v>1</v>
       </c>
-      <c r="M68" s="4"/>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N68" s="6"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>85</v>
       </c>
@@ -3509,9 +4015,16 @@
       <c r="L69">
         <v>1</v>
       </c>
-      <c r="M69" s="4"/>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N69" s="6"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>86</v>
       </c>
@@ -3550,9 +4063,16 @@
       <c r="L70">
         <v>1</v>
       </c>
-      <c r="M70" s="4"/>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N70" s="6"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>87</v>
       </c>
@@ -3591,9 +4111,16 @@
       <c r="L71">
         <v>1</v>
       </c>
-      <c r="M71" s="4"/>
-    </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N71" s="6"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>88</v>
       </c>
@@ -3632,9 +4159,16 @@
       <c r="L72">
         <v>1</v>
       </c>
-      <c r="M72" s="4"/>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N72" s="6"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>99</v>
       </c>
@@ -3673,9 +4207,16 @@
       <c r="L73">
         <v>1</v>
       </c>
-      <c r="M73" s="4"/>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N73" s="6"/>
+      <c r="O73" s="4"/>
+      <c r="P73" s="4"/>
+      <c r="Q73" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R73" s="4"/>
+      <c r="S73" s="4"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>100</v>
       </c>
@@ -3714,9 +4255,16 @@
       <c r="L74">
         <v>1</v>
       </c>
-      <c r="M74" s="4"/>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N74" s="6"/>
+      <c r="O74" s="4"/>
+      <c r="P74" s="4"/>
+      <c r="Q74" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R74" s="4"/>
+      <c r="S74" s="4"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>101</v>
       </c>
@@ -3755,9 +4303,16 @@
       <c r="L75">
         <v>1</v>
       </c>
-      <c r="M75" s="4"/>
-    </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N75" s="6"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>112</v>
       </c>
@@ -3796,9 +4351,16 @@
       <c r="L76">
         <v>1</v>
       </c>
-      <c r="M76" s="4"/>
-    </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N76" s="6"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>115</v>
       </c>
@@ -3837,9 +4399,16 @@
       <c r="L77">
         <v>1</v>
       </c>
-      <c r="M77" s="4"/>
-    </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N77" s="6"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>118</v>
       </c>
@@ -3878,9 +4447,16 @@
       <c r="L78">
         <v>1</v>
       </c>
-      <c r="M78" s="4"/>
-    </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N78" s="6"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>125</v>
       </c>
@@ -3919,9 +4495,16 @@
       <c r="L79">
         <v>1</v>
       </c>
-      <c r="M79" s="4"/>
-    </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N79" s="6"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>126</v>
       </c>
@@ -3960,9 +4543,16 @@
       <c r="L80">
         <v>1</v>
       </c>
-      <c r="M80" s="4"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N80" s="6"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R80" s="4"/>
+      <c r="S80" s="4"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>138</v>
       </c>
@@ -4001,9 +4591,12 @@
       <c r="L81">
         <v>1</v>
       </c>
-      <c r="M81" s="4"/>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N81" s="6"/>
+      <c r="Q81" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>139</v>
       </c>
@@ -4042,9 +4635,12 @@
       <c r="L82">
         <v>1</v>
       </c>
-      <c r="M82" s="4"/>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N82" s="6"/>
+      <c r="Q82" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>140</v>
       </c>
@@ -4083,9 +4679,12 @@
       <c r="L83">
         <v>1</v>
       </c>
-      <c r="M83" s="4"/>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N83" s="6"/>
+      <c r="Q83" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>141</v>
       </c>
@@ -4124,9 +4723,12 @@
       <c r="L84">
         <v>1</v>
       </c>
-      <c r="M84" s="4"/>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N84" s="6"/>
+      <c r="Q84" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>142</v>
       </c>
@@ -4165,9 +4767,12 @@
       <c r="L85">
         <v>1</v>
       </c>
-      <c r="M85" s="4"/>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N85" s="6"/>
+      <c r="Q85" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>152</v>
       </c>
@@ -4206,9 +4811,12 @@
       <c r="L86">
         <v>1</v>
       </c>
-      <c r="M86" s="4"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N86" s="6"/>
+      <c r="Q86" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>153</v>
       </c>
@@ -4247,9 +4855,12 @@
       <c r="L87">
         <v>1</v>
       </c>
-      <c r="M87" s="4"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N87" s="6"/>
+      <c r="Q87" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>154</v>
       </c>
@@ -4288,9 +4899,12 @@
       <c r="L88">
         <v>1</v>
       </c>
-      <c r="M88" s="4"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N88" s="6"/>
+      <c r="Q88" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>155</v>
       </c>
@@ -4329,9 +4943,12 @@
       <c r="L89">
         <v>1</v>
       </c>
-      <c r="M89" s="4"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N89" s="6"/>
+      <c r="Q89" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2</v>
       </c>
@@ -4370,9 +4987,14 @@
       <c r="L90">
         <v>2</v>
       </c>
-      <c r="M90" s="4"/>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N90" s="6"/>
+      <c r="O90" s="4"/>
+      <c r="P90" s="4"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="4"/>
+      <c r="S90" s="4"/>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>11</v>
       </c>
@@ -4411,9 +5033,14 @@
       <c r="L91">
         <v>2</v>
       </c>
-      <c r="M91" s="4"/>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N91" s="6"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="4"/>
+      <c r="S91" s="4"/>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>15</v>
       </c>
@@ -4452,9 +5079,14 @@
       <c r="L92">
         <v>2</v>
       </c>
-      <c r="M92" s="4"/>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N92" s="6"/>
+      <c r="O92" s="4"/>
+      <c r="P92" s="4"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4"/>
+      <c r="S92" s="4"/>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>16</v>
       </c>
@@ -4493,9 +5125,14 @@
       <c r="L93">
         <v>2</v>
       </c>
-      <c r="M93" s="4"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N93" s="6"/>
+      <c r="O93" s="4"/>
+      <c r="P93" s="4"/>
+      <c r="Q93" s="4"/>
+      <c r="R93" s="4"/>
+      <c r="S93" s="4"/>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>17</v>
       </c>
@@ -4534,9 +5171,14 @@
       <c r="L94">
         <v>2</v>
       </c>
-      <c r="M94" s="4"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N94" s="6"/>
+      <c r="O94" s="4"/>
+      <c r="P94" s="4"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4"/>
+      <c r="S94" s="4"/>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>18</v>
       </c>
@@ -4575,9 +5217,14 @@
       <c r="L95">
         <v>2</v>
       </c>
-      <c r="M95" s="4"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N95" s="6"/>
+      <c r="O95" s="4"/>
+      <c r="P95" s="4"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+      <c r="S95" s="4"/>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>19</v>
       </c>
@@ -4616,9 +5263,14 @@
       <c r="L96">
         <v>2</v>
       </c>
-      <c r="M96" s="4"/>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N96" s="6"/>
+      <c r="O96" s="4"/>
+      <c r="P96" s="4"/>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="4"/>
+      <c r="S96" s="4"/>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>20</v>
       </c>
@@ -4657,9 +5309,14 @@
       <c r="L97">
         <v>2</v>
       </c>
-      <c r="M97" s="4"/>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N97" s="6"/>
+      <c r="O97" s="4"/>
+      <c r="P97" s="4"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="4"/>
+      <c r="S97" s="4"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>21</v>
       </c>
@@ -4698,9 +5355,14 @@
       <c r="L98">
         <v>2</v>
       </c>
-      <c r="M98" s="4"/>
-    </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N98" s="6"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="4"/>
+      <c r="R98" s="4"/>
+      <c r="S98" s="4"/>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>22</v>
       </c>
@@ -4739,9 +5401,14 @@
       <c r="L99">
         <v>2</v>
       </c>
-      <c r="M99" s="4"/>
-    </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N99" s="6"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="4"/>
+      <c r="R99" s="4"/>
+      <c r="S99" s="4"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>23</v>
       </c>
@@ -4780,9 +5447,14 @@
       <c r="L100">
         <v>2</v>
       </c>
-      <c r="M100" s="4"/>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N100" s="6"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4"/>
+      <c r="S100" s="4"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>24</v>
       </c>
@@ -4821,9 +5493,14 @@
       <c r="L101">
         <v>2</v>
       </c>
-      <c r="M101" s="4"/>
-    </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N101" s="6"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="4"/>
+      <c r="S101" s="4"/>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>28</v>
       </c>
@@ -4862,9 +5539,14 @@
       <c r="L102">
         <v>2</v>
       </c>
-      <c r="M102" s="4"/>
-    </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N102" s="6"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>39</v>
       </c>
@@ -4903,9 +5585,14 @@
       <c r="L103">
         <v>2</v>
       </c>
-      <c r="M103" s="4"/>
-    </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N103" s="6"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>41</v>
       </c>
@@ -4944,9 +5631,14 @@
       <c r="L104">
         <v>2</v>
       </c>
-      <c r="M104" s="4"/>
-    </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N104" s="6"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+      <c r="S104" s="4"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>116</v>
       </c>
@@ -4985,9 +5677,14 @@
       <c r="L105">
         <v>2</v>
       </c>
-      <c r="M105" s="4"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N105" s="6"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4"/>
+      <c r="S105" s="4"/>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>117</v>
       </c>
@@ -5026,9 +5723,14 @@
       <c r="L106">
         <v>2</v>
       </c>
-      <c r="M106" s="4"/>
-    </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N106" s="6"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="4"/>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>119</v>
       </c>
@@ -5067,9 +5769,14 @@
       <c r="L107">
         <v>2</v>
       </c>
-      <c r="M107" s="4"/>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N107" s="6"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>120</v>
       </c>
@@ -5108,9 +5815,14 @@
       <c r="L108">
         <v>2</v>
       </c>
-      <c r="M108" s="4"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N108" s="6"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>127</v>
       </c>
@@ -5149,9 +5861,14 @@
       <c r="L109">
         <v>2</v>
       </c>
-      <c r="M109" s="4"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N109" s="6"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="4"/>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>128</v>
       </c>
@@ -5190,9 +5907,14 @@
       <c r="L110">
         <v>2</v>
       </c>
-      <c r="M110" s="4"/>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N110" s="6"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+      <c r="S110" s="4"/>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>129</v>
       </c>
@@ -5231,9 +5953,14 @@
       <c r="L111">
         <v>2</v>
       </c>
-      <c r="M111" s="4"/>
-    </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N111" s="6"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+      <c r="S111" s="4"/>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>131</v>
       </c>
@@ -5272,9 +5999,9 @@
       <c r="L112">
         <v>2</v>
       </c>
-      <c r="M112" s="4"/>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>132</v>
       </c>
@@ -5313,9 +6040,9 @@
       <c r="L113">
         <v>2</v>
       </c>
-      <c r="M113" s="4"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>92</v>
       </c>
@@ -5354,9 +6081,17 @@
       <c r="L114">
         <v>11</v>
       </c>
-      <c r="M114" s="4"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M114" s="5"/>
+      <c r="N114" s="6"/>
+      <c r="O114" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4"/>
+      <c r="S114" s="4"/>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>105</v>
       </c>
@@ -5395,9 +6130,17 @@
       <c r="L115">
         <v>11</v>
       </c>
-      <c r="M115" s="4"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M115" s="5"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="4"/>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>3</v>
       </c>
@@ -5436,11 +6179,21 @@
       <c r="L116">
         <v>4</v>
       </c>
-      <c r="M116" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M116" s="5"/>
+      <c r="N116" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O116" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P116" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4"/>
+      <c r="S116" s="4"/>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>4</v>
       </c>
@@ -5479,11 +6232,21 @@
       <c r="L117">
         <v>4</v>
       </c>
-      <c r="M117" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M117" s="5"/>
+      <c r="N117" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O117" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P117" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q117" s="4"/>
+      <c r="R117" s="4"/>
+      <c r="S117" s="4"/>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>81</v>
       </c>
@@ -5522,11 +6285,21 @@
       <c r="L118">
         <v>4</v>
       </c>
-      <c r="M118" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M118" s="5"/>
+      <c r="N118" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O118" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P118" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="4"/>
+      <c r="S118" s="4"/>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>82</v>
       </c>
@@ -5565,11 +6338,21 @@
       <c r="L119">
         <v>4</v>
       </c>
-      <c r="M119" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M119" s="5"/>
+      <c r="N119" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O119" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P119" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4"/>
+      <c r="S119" s="4"/>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>89</v>
       </c>
@@ -5608,11 +6391,21 @@
       <c r="L120">
         <v>4</v>
       </c>
-      <c r="M120" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M120" s="5"/>
+      <c r="N120" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O120" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P120" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q120" s="4"/>
+      <c r="R120" s="4"/>
+      <c r="S120" s="4"/>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>25</v>
       </c>
@@ -5651,9 +6444,16 @@
       <c r="L121">
         <v>3</v>
       </c>
-      <c r="M121" s="4"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N121" s="6"/>
+      <c r="O121" s="4"/>
+      <c r="P121" s="4"/>
+      <c r="Q121" s="4"/>
+      <c r="R121" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S121" s="4"/>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>42</v>
       </c>
@@ -5692,9 +6492,16 @@
       <c r="L122">
         <v>3</v>
       </c>
-      <c r="M122" s="4"/>
-    </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N122" s="6"/>
+      <c r="O122" s="4"/>
+      <c r="P122" s="4"/>
+      <c r="Q122" s="4"/>
+      <c r="R122" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S122" s="4"/>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>43</v>
       </c>
@@ -5733,9 +6540,16 @@
       <c r="L123">
         <v>3</v>
       </c>
-      <c r="M123" s="4"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N123" s="6"/>
+      <c r="O123" s="4"/>
+      <c r="P123" s="4"/>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S123" s="4"/>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>45</v>
       </c>
@@ -5774,9 +6588,16 @@
       <c r="L124">
         <v>3</v>
       </c>
-      <c r="M124" s="4"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N124" s="6"/>
+      <c r="O124" s="4"/>
+      <c r="P124" s="4"/>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S124" s="4"/>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>46</v>
       </c>
@@ -5815,9 +6636,16 @@
       <c r="L125">
         <v>3</v>
       </c>
-      <c r="M125" s="4"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N125" s="6"/>
+      <c r="O125" s="4"/>
+      <c r="P125" s="4"/>
+      <c r="Q125" s="4"/>
+      <c r="R125" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S125" s="4"/>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>47</v>
       </c>
@@ -5856,9 +6684,16 @@
       <c r="L126">
         <v>3</v>
       </c>
-      <c r="M126" s="4"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N126" s="6"/>
+      <c r="O126" s="4"/>
+      <c r="P126" s="4"/>
+      <c r="Q126" s="4"/>
+      <c r="R126" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S126" s="4"/>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>48</v>
       </c>
@@ -5897,9 +6732,16 @@
       <c r="L127">
         <v>3</v>
       </c>
-      <c r="M127" s="4"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N127" s="6"/>
+      <c r="O127" s="4"/>
+      <c r="P127" s="4"/>
+      <c r="Q127" s="4"/>
+      <c r="R127" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S127" s="4"/>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>51</v>
       </c>
@@ -5938,9 +6780,16 @@
       <c r="L128">
         <v>3</v>
       </c>
-      <c r="M128" s="4"/>
-    </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N128" s="6"/>
+      <c r="O128" s="4"/>
+      <c r="P128" s="4"/>
+      <c r="Q128" s="4"/>
+      <c r="R128" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S128" s="4"/>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>113</v>
       </c>
@@ -5979,9 +6828,16 @@
       <c r="L129">
         <v>3</v>
       </c>
-      <c r="M129" s="4"/>
-    </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N129" s="6"/>
+      <c r="O129" s="4"/>
+      <c r="P129" s="4"/>
+      <c r="Q129" s="4"/>
+      <c r="R129" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S129" s="4"/>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>114</v>
       </c>
@@ -6020,9 +6876,16 @@
       <c r="L130">
         <v>3</v>
       </c>
-      <c r="M130" s="4"/>
-    </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N130" s="6"/>
+      <c r="O130" s="4"/>
+      <c r="P130" s="4"/>
+      <c r="Q130" s="4"/>
+      <c r="R130" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S130" s="4"/>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>123</v>
       </c>
@@ -6061,9 +6924,16 @@
       <c r="L131">
         <v>3</v>
       </c>
-      <c r="M131" s="4"/>
-    </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N131" s="6"/>
+      <c r="O131" s="4"/>
+      <c r="P131" s="4"/>
+      <c r="Q131" s="4"/>
+      <c r="R131" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S131" s="4"/>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>124</v>
       </c>
@@ -6102,9 +6972,16 @@
       <c r="L132">
         <v>3</v>
       </c>
-      <c r="M132" s="4"/>
-    </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N132" s="6"/>
+      <c r="O132" s="4"/>
+      <c r="P132" s="4"/>
+      <c r="Q132" s="4"/>
+      <c r="R132" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="S132" s="4"/>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>40</v>
       </c>
@@ -6143,9 +7020,17 @@
       <c r="L133">
         <v>12</v>
       </c>
-      <c r="M133" s="4"/>
-    </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M133" s="5"/>
+      <c r="N133" s="6"/>
+      <c r="O133" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P133" s="4"/>
+      <c r="Q133" s="4"/>
+      <c r="R133" s="4"/>
+      <c r="S133" s="4"/>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>136</v>
       </c>
@@ -6184,9 +7069,9 @@
       <c r="L134">
         <v>88</v>
       </c>
-      <c r="M134" s="4"/>
-    </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>149</v>
       </c>
@@ -6225,9 +7110,9 @@
       <c r="L135">
         <v>88</v>
       </c>
-      <c r="M135" s="4"/>
-    </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>145</v>
       </c>
@@ -6266,11 +7151,11 @@
       <c r="L136">
         <v>85</v>
       </c>
-      <c r="M136" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N136" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>146</v>
       </c>
@@ -6309,11 +7194,11 @@
       <c r="L137">
         <v>85</v>
       </c>
-      <c r="M137" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N137" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>157</v>
       </c>
@@ -6352,11 +7237,11 @@
       <c r="L138">
         <v>85</v>
       </c>
-      <c r="M138" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N138" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>158</v>
       </c>
@@ -6395,11 +7280,11 @@
       <c r="L139">
         <v>85</v>
       </c>
-      <c r="M139" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N139" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>159</v>
       </c>
@@ -6438,11 +7323,11 @@
       <c r="L140">
         <v>85</v>
       </c>
-      <c r="M140" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N140" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>160</v>
       </c>
@@ -6481,11 +7366,11 @@
       <c r="L141">
         <v>85</v>
       </c>
-      <c r="M141" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N141" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>27</v>
       </c>
@@ -6524,9 +7409,21 @@
       <c r="L142">
         <v>10</v>
       </c>
-      <c r="M142" s="4"/>
-    </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M142" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N142" s="6"/>
+      <c r="O142" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P142" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q142" s="4"/>
+      <c r="R142" s="4"/>
+      <c r="S142" s="4"/>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>64</v>
       </c>
@@ -6565,9 +7462,17 @@
       <c r="L143">
         <v>13</v>
       </c>
-      <c r="M143" s="4"/>
-    </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M143" s="5"/>
+      <c r="N143" s="6"/>
+      <c r="O143" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P143" s="4"/>
+      <c r="Q143" s="4"/>
+      <c r="R143" s="4"/>
+      <c r="S143" s="4"/>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>65</v>
       </c>
@@ -6606,9 +7511,17 @@
       <c r="L144">
         <v>13</v>
       </c>
-      <c r="M144" s="4"/>
-    </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M144" s="5"/>
+      <c r="N144" s="6"/>
+      <c r="O144" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P144" s="4"/>
+      <c r="Q144" s="4"/>
+      <c r="R144" s="4"/>
+      <c r="S144" s="4"/>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>102</v>
       </c>
@@ -6647,9 +7560,17 @@
       <c r="L145">
         <v>13</v>
       </c>
-      <c r="M145" s="4"/>
-    </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M145" s="5"/>
+      <c r="N145" s="6"/>
+      <c r="O145" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P145" s="4"/>
+      <c r="Q145" s="4"/>
+      <c r="R145" s="4"/>
+      <c r="S145" s="4"/>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>106</v>
       </c>
@@ -6688,9 +7609,17 @@
       <c r="L146">
         <v>13</v>
       </c>
-      <c r="M146" s="4"/>
-    </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M146" s="5"/>
+      <c r="N146" s="6"/>
+      <c r="O146" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P146" s="4"/>
+      <c r="Q146" s="4"/>
+      <c r="R146" s="4"/>
+      <c r="S146" s="4"/>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>109</v>
       </c>
@@ -6729,9 +7658,17 @@
       <c r="L147">
         <v>13</v>
       </c>
-      <c r="M147" s="4"/>
-    </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M147" s="5"/>
+      <c r="N147" s="6"/>
+      <c r="O147" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P147" s="4"/>
+      <c r="Q147" s="4"/>
+      <c r="R147" s="4"/>
+      <c r="S147" s="4"/>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>121</v>
       </c>
@@ -6770,9 +7707,17 @@
       <c r="L148">
         <v>13</v>
       </c>
-      <c r="M148" s="4"/>
-    </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M148" s="5"/>
+      <c r="N148" s="6"/>
+      <c r="O148" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P148" s="4"/>
+      <c r="Q148" s="4"/>
+      <c r="R148" s="4"/>
+      <c r="S148" s="4"/>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>147</v>
       </c>
@@ -6811,9 +7756,9 @@
       <c r="L149">
         <v>13</v>
       </c>
-      <c r="M149" s="4"/>
-    </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N149" s="6"/>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>33</v>
       </c>
@@ -6852,11 +7797,21 @@
       <c r="L150">
         <v>7</v>
       </c>
-      <c r="M150" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M150" s="5"/>
+      <c r="N150" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O150" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P150" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q150" s="4"/>
+      <c r="R150" s="4"/>
+      <c r="S150" s="4"/>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>34</v>
       </c>
@@ -6895,11 +7850,21 @@
       <c r="L151">
         <v>7</v>
       </c>
-      <c r="M151" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M151" s="5"/>
+      <c r="N151" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O151" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P151" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q151" s="4"/>
+      <c r="R151" s="4"/>
+      <c r="S151" s="4"/>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>35</v>
       </c>
@@ -6938,11 +7903,21 @@
       <c r="L152">
         <v>7</v>
       </c>
-      <c r="M152" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M152" s="5"/>
+      <c r="N152" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O152" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P152" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q152" s="4"/>
+      <c r="R152" s="4"/>
+      <c r="S152" s="4"/>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>37</v>
       </c>
@@ -6981,11 +7956,21 @@
       <c r="L153">
         <v>7</v>
       </c>
-      <c r="M153" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M153" s="5"/>
+      <c r="N153" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O153" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P153" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q153" s="4"/>
+      <c r="R153" s="4"/>
+      <c r="S153" s="4"/>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>29</v>
       </c>
@@ -7024,11 +8009,19 @@
       <c r="L154">
         <v>6</v>
       </c>
-      <c r="M154" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M154" s="5"/>
+      <c r="N154" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O154" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P154" s="4"/>
+      <c r="Q154" s="4"/>
+      <c r="R154" s="4"/>
+      <c r="S154" s="4"/>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>30</v>
       </c>
@@ -7067,11 +8060,19 @@
       <c r="L155">
         <v>6</v>
       </c>
-      <c r="M155" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="M155" s="5"/>
+      <c r="N155" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O155" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P155" s="4"/>
+      <c r="Q155" s="4"/>
+      <c r="R155" s="4"/>
+      <c r="S155" s="4"/>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>103</v>
       </c>
@@ -7110,9 +8111,14 @@
       <c r="L156">
         <v>27</v>
       </c>
-      <c r="M156" s="4"/>
-    </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N156" s="6"/>
+      <c r="O156" s="4"/>
+      <c r="P156" s="4"/>
+      <c r="Q156" s="4"/>
+      <c r="R156" s="4"/>
+      <c r="S156" s="4"/>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>52</v>
       </c>
@@ -7151,9 +8157,14 @@
       <c r="L157">
         <v>22</v>
       </c>
-      <c r="M157" s="4"/>
-    </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N157" s="6"/>
+      <c r="O157" s="4"/>
+      <c r="P157" s="4"/>
+      <c r="Q157" s="4"/>
+      <c r="R157" s="4"/>
+      <c r="S157" s="4"/>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>122</v>
       </c>
@@ -7192,9 +8203,14 @@
       <c r="L158">
         <v>87</v>
       </c>
-      <c r="M158" s="4"/>
-    </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N158" s="6"/>
+      <c r="O158" s="4"/>
+      <c r="P158" s="4"/>
+      <c r="Q158" s="4"/>
+      <c r="R158" s="4"/>
+      <c r="S158" s="4"/>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>14</v>
       </c>
@@ -7233,9 +8249,14 @@
       <c r="L159">
         <v>23</v>
       </c>
-      <c r="M159" s="4"/>
-    </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N159" s="6"/>
+      <c r="O159" s="4"/>
+      <c r="P159" s="4"/>
+      <c r="Q159" s="4"/>
+      <c r="R159" s="4"/>
+      <c r="S159" s="4"/>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>66</v>
       </c>
@@ -7274,9 +8295,14 @@
       <c r="L160">
         <v>23</v>
       </c>
-      <c r="M160" s="4"/>
-    </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="N160" s="6"/>
+      <c r="O160" s="4"/>
+      <c r="P160" s="4"/>
+      <c r="Q160" s="4"/>
+      <c r="R160" s="4"/>
+      <c r="S160" s="4"/>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>13</v>
       </c>
@@ -7315,7 +8341,12 @@
       <c r="L161">
         <v>18</v>
       </c>
-      <c r="M161" s="4"/>
+      <c r="N161" s="6"/>
+      <c r="O161" s="4"/>
+      <c r="P161" s="4"/>
+      <c r="Q161" s="4"/>
+      <c r="R161" s="4"/>
+      <c r="S161" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
